--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,22 +3316,22 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46031.22916666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
         <v>3.55</v>
@@ -823,10 +823,10 @@
         <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.12</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,22 +3435,22 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46031.42361111111</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -790,22 +790,22 @@
         <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
         <v>6.25</v>
@@ -814,13 +814,13 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -829,7 +829,7 @@
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
         <v>1.28</v>
@@ -838,13 +838,13 @@
         <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3524,40 +3524,40 @@
         <v>2.05</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA26" t="n">
         <v>1.62</v>
@@ -3572,16 +3572,16 @@
         <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -793,7 +793,7 @@
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -802,13 +802,13 @@
         <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -829,7 +829,7 @@
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AD3" t="n">
         <v>1.28</v>
@@ -841,10 +841,10 @@
         <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>5.08</v>
+        <v>5.49</v>
       </c>
       <c r="P15" t="n">
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
         <v>1.32</v>
@@ -2230,16 +2230,16 @@
         <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
         <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.58</v>
+        <v>3.93</v>
       </c>
       <c r="AA15" t="n">
         <v>1.7</v>
@@ -2260,19 +2260,19 @@
         <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.64</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.67</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>3.44</v>
+        <v>2.39</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.49</v>
+        <v>1.77</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.6875</v>
@@ -3643,40 +3643,40 @@
         <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA27" t="n">
         <v>1.9</v>
@@ -3685,22 +3685,22 @@
         <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.69791666666</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46031.50347222222</v>
+        <v>46031.5</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46031.58333333334</v>
+        <v>46031.5</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46031.58333333334</v>
+        <v>46031.5</v>
       </c>
     </row>
     <row r="16">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46031.60416666666</v>
+        <v>46031.50347222222</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46031.66666666666</v>
+        <v>46031.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46031.66666666666</v>
+        <v>46031.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46031.66666666666</v>
+        <v>46031.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46031.66666666666</v>
+        <v>46031.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46031.6875</v>
+        <v>46031.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46031.6875</v>
+        <v>46031.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46031.6875</v>
+        <v>46031.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.64</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.39</v>
-      </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>5.59</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.58</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46031.6875</v>
+        <v>46031.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V27" t="n">
-        <v>6.95</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.04</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.61</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46031.69791666666</v>
+        <v>46031.6875</v>
       </c>
     </row>
     <row r="28">
@@ -3712,116 +3712,592 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ascoli</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ternana</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46031.6875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Audace Cerignola</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Potenza Calcio</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46031.6875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>46031.6875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ross County</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Partick Thistle</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>46031.69791666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Getafe CF</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="3" t="n">
+      <c r="L32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>46031.70833333334</v>
       </c>
     </row>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
         <v>6.75</v>
@@ -698,28 +698,28 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG2" t="n">
         <v>1.24</v>
@@ -778,31 +778,31 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
         <v>1.4</v>
@@ -823,13 +823,13 @@
         <v>3.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="AD3" t="n">
         <v>1.28</v>
@@ -841,10 +841,10 @@
         <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.64</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>9.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.49</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>2.39</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
-        <v>9.6</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4.58</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>2.49</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
         <v>3.56</v>
@@ -823,10 +823,10 @@
         <v>3.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.19</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.93</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4128,7 +4128,7 @@
         <v>2.74</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
         <v>2.78</v>
@@ -4164,7 +4164,7 @@
         <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE31" t="n">
         <v>1.67</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>6.65</v>
+        <v>6.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>2.44</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,22 +1055,22 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>5.49</v>
+        <v>2.94</v>
       </c>
       <c r="P18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.35</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.78</v>
+        <v>5.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>3.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>4.06</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,58 +3039,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.11</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
         <v>1.6</v>
@@ -3102,10 +3102,10 @@
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>4.59</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.48</v>
       </c>
-      <c r="V24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AF24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>4.59</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.63</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>2.41</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
-        <v>9.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
         <v>3.3</v>
@@ -823,10 +823,10 @@
         <v>3.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.03</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,22 +1055,22 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>5.49</v>
+        <v>2.94</v>
       </c>
       <c r="P19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.35</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.78</v>
+        <v>5.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.44</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.13</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
         <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,58 +3396,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="P25" t="n">
         <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.11</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z25" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
         <v>1.6</v>
@@ -3459,10 +3459,10 @@
         <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
         <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
         <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2682,43 +2682,43 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="P19" t="n">
         <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
       <c r="R19" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="U19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
         <v>1.57</v>
@@ -2727,16 +2727,16 @@
         <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
         <v>2.28</v>
@@ -2748,7 +2748,7 @@
         <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.22</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V24" t="n">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
         <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.23</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,22 +1174,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>3.58</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>3.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF23" t="n">
         <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.89</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
         <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>2.44</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.23</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.4</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3881,31 +3881,31 @@
         <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
@@ -3923,7 +3923,7 @@
         <v>1.48</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="AD29" t="n">
         <v>1.2</v>
@@ -3935,10 +3935,10 @@
         <v>1.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>2.23</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,19 +787,19 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
         <v>2.65</v>
@@ -808,7 +808,7 @@
         <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -817,10 +817,10 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -829,19 +829,19 @@
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF3" t="n">
         <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
         <v>1.4</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,22 +1174,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1858,34 +1858,34 @@
         <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.52</v>
@@ -1894,28 +1894,28 @@
         <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>2.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
         <v>1.77</v>
@@ -2507,10 +2507,10 @@
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2691,34 +2691,34 @@
         <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.99</v>
+        <v>5.41</v>
       </c>
       <c r="R19" t="n">
         <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T19" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
         <v>1.57</v>
@@ -2727,28 +2727,28 @@
         <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AF19" t="n">
         <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2929,40 +2929,40 @@
         <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
         <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
         <v>3.64</v>
       </c>
       <c r="T21" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
         <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
         <v>1.55</v>
@@ -2983,7 +2983,7 @@
         <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
         <v>1.75</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>3.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.4</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.48</v>
       </c>
-      <c r="V22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.89</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.22</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.19</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3887,13 +3887,13 @@
         <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.74</v>
+        <v>3.26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="T29" t="n">
         <v>3.1</v>
@@ -3935,7 +3935,7 @@
         <v>1.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AH29" t="n">
         <v>1.53</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4119,13 +4119,13 @@
         <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
@@ -4146,13 +4146,13 @@
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="AA31" t="n">
         <v>1.9</v>
@@ -4161,10 +4161,10 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE31" t="n">
         <v>1.67</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,22 +1174,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.74</v>
+        <v>5.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
         <v>9.1</v>
@@ -1885,37 +1885,37 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.78</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q14" t="n">
-        <v>5.89</v>
+        <v>3.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
         <v>9.1</v>
@@ -2123,37 +2123,37 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
         <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>4.59</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.09</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.19</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.26</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.55</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>3.36</v>
+        <v>2.41</v>
       </c>
       <c r="T27" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>4.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,55 +3753,55 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.95</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.41</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="Z29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AD29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,37 +787,37 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.06</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
         <v>3.4</v>
@@ -829,13 +829,13 @@
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AD3" t="n">
         <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF3" t="n">
         <v>2.1</v>
@@ -844,7 +844,7 @@
         <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.78</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q12" t="n">
-        <v>5.89</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2498,7 +2498,7 @@
         <v>2.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
         <v>1.77</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.76</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
         <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>4.06</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.09</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.19</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>4.45</v>
       </c>
       <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.11</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z25" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>3.36</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="V27" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AD27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.55</v>
+        <v>4.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>2.36</v>
       </c>
       <c r="T29" t="n">
-        <v>2.51</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>4.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.95</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4122,10 +4122,10 @@
         <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
@@ -4134,10 +4134,10 @@
         <v>2.78</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
         <v>6.95</v>
@@ -4167,13 +4167,13 @@
         <v>1.32</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
         <v>1.27</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.78</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="M13" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>4.6</v>
+        <v>3.48</v>
       </c>
       <c r="P13" t="n">
         <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>3.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
         <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>2.79</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.18</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>3.8</v>
       </c>
       <c r="U17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.44</v>
       </c>
-      <c r="V17" t="n">
-        <v>6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.76</v>
+        <v>5.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>3.36</v>
+        <v>2.41</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>4.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>4.72</v>
       </c>
       <c r="R28" t="n">
         <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="U28" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
         <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.72</v>
+        <v>2.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.36</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="U29" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.52</v>
+        <v>4.15</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -793,13 +793,13 @@
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
         <v>2.73</v>
@@ -808,7 +808,7 @@
         <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -817,10 +817,10 @@
         <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -832,19 +832,19 @@
         <v>3.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
         <v>1.65</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.48</v>
+        <v>2.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.74</v>
+        <v>5.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>2.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>4.06</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.09</v>
+        <v>3.76</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="T22" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W22" t="n">
         <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>4.59</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W24" t="n">
         <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
         <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>4.68</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA27" t="n">
         <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="O28" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.72</v>
+        <v>4.61</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="T28" t="n">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="U28" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>2.61</v>
+        <v>2.97</v>
       </c>
       <c r="P30" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.62</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.34</v>
+        <v>4.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.78</v>
       </c>
-      <c r="AF30" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.24</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.33</v>
+        <v>5.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.13</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.76</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
         <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.09</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.19</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>3.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF24" t="n">
         <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.5</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,64 +3515,64 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
@@ -3581,7 +3581,7 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.68</v>
+        <v>2.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>3.36</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.25</v>
       </c>
-      <c r="V27" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.55</v>
+        <v>4.68</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.15</v>
+        <v>2.56</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>4.45</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -4000,16 +4000,16 @@
         <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="P30" t="n">
         <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
         <v>2.41</v>
@@ -4042,7 +4042,7 @@
         <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="AD30" t="n">
         <v>1.2</v>
@@ -4051,13 +4051,13 @@
         <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,19 +787,19 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="P3" t="n">
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
         <v>2.73</v>
@@ -811,13 +811,13 @@
         <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
         <v>3.58</v>
@@ -1858,19 +1858,19 @@
         <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
         <v>3.92</v>
@@ -1882,7 +1882,7 @@
         <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.12</v>
@@ -1894,16 +1894,16 @@
         <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
         <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
         <v>2.21</v>
@@ -1912,10 +1912,10 @@
         <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -2096,22 +2096,22 @@
         <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.86</v>
+        <v>6.44</v>
       </c>
       <c r="R14" t="n">
         <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
         <v>1.23</v>
@@ -2120,7 +2120,7 @@
         <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
@@ -2147,13 +2147,13 @@
         <v>2.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG14" t="n">
         <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2215,10 +2215,10 @@
         <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>5.24</v>
+        <v>5.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
         <v>2.88</v>
@@ -2233,7 +2233,7 @@
         <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
         <v>13</v>
@@ -2242,7 +2242,7 @@
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
         <v>1.72</v>
@@ -2251,13 +2251,13 @@
         <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="AD15" t="n">
         <v>1.06</v>
@@ -2272,7 +2272,7 @@
         <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2453,19 +2453,19 @@
         <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="P17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T17" t="n">
         <v>4</v>
@@ -2474,13 +2474,13 @@
         <v>1.16</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
         <v>1.57</v>
@@ -2489,28 +2489,28 @@
         <v>2.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="AD17" t="n">
         <v>1.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.09</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.19</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>3.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.48</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="P26" t="n">
         <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.76</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
         <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3658,31 +3658,31 @@
         <v>3.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="U27" t="n">
         <v>1.54</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W27" t="n">
         <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AC27" t="n">
         <v>2.35</v>
@@ -3697,7 +3697,7 @@
         <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
         <v>1.36</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N28" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="O28" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.12</v>
+        <v>2.56</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="O29" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
         <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -4000,13 +4000,13 @@
         <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
@@ -4015,10 +4015,10 @@
         <v>2.41</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
         <v>9.300000000000001</v>
@@ -4036,13 +4036,13 @@
         <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="AD30" t="n">
         <v>1.2</v>
@@ -4051,13 +4051,13 @@
         <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4119,13 +4119,13 @@
         <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="P31" t="n">
         <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
@@ -4137,10 +4137,10 @@
         <v>2.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
@@ -4152,7 +4152,7 @@
         <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA31" t="n">
         <v>1.9</v>
@@ -4161,10 +4161,10 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
         <v>1.75</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>3.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.44</v>
+        <v>4.34</v>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.89</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
         <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.44</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.13</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="M25" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O25" t="n">
         <v>4</v>
       </c>
-      <c r="N25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.59</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
         <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB25" t="n">
         <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="P26" t="n">
         <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="W26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.11</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
         <v>1.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.55</v>
+        <v>4.62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>3.36</v>
+        <v>2.34</v>
       </c>
       <c r="T27" t="n">
-        <v>2.51</v>
+        <v>3.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>5.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>4.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
         <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.62</v>
+        <v>3.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
         <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.03</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.61</v>
+        <v>2.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="U29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.53</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.41</v>
-      </c>
       <c r="T30" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,22 +1055,22 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>5.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.44</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="S13" t="n">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AF13" t="n">
         <v>1.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.99</v>
+        <v>1.18</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>5.26</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>6.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
         <v>1.47</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.18</v>
+        <v>1.99</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>4.59</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.63</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
         <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>3.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>1.48</v>
       </c>
-      <c r="V24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
         <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
         <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
         <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O27" t="n">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M30" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N30" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="O30" t="n">
-        <v>2.58</v>
+        <v>2.81</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W30" t="n">
         <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.28</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.81</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M8" t="n">
         <v>2.8</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1409,37 +1409,37 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46031.38541666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46031.41666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="M13" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>5.26</v>
+        <v>3.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>4.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
         <v>13</v>
@@ -2007,34 +2007,34 @@
         <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC13" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.27</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.34</v>
+        <v>6.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>2.62</v>
       </c>
       <c r="M15" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.44</v>
+        <v>3.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="T15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.7</v>
+        <v>4.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>3.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.89</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
         <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>4.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
         <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3652,16 +3652,16 @@
         <v>4.61</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
         <v>2.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
         <v>7.2</v>
@@ -3673,7 +3673,7 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
         <v>2.92</v>
@@ -3688,13 +3688,13 @@
         <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
         <v>1.26</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
         <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.55</v>
+        <v>3.31</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.09</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.62</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="AG30" t="n">
         <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4119,13 +4119,13 @@
         <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
@@ -4134,19 +4134,19 @@
         <v>2.78</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.28</v>
@@ -4161,10 +4161,10 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE31" t="n">
         <v>1.75</v>
@@ -4176,7 +4176,7 @@
         <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46031.69791666666</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,40 +787,40 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.9</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.94</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.24</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -829,22 +829,22 @@
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>3.16</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>5.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M7" t="n">
         <v>2.8</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.75</v>
-      </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>4.53</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.53</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.06</v>
+        <v>3.16</v>
       </c>
       <c r="T8" t="n">
-        <v>4.33</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.04</v>
+        <v>3.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.44</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>2.37</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>5.26</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>4.92</v>
       </c>
       <c r="O13" t="n">
-        <v>3.27</v>
+        <v>2.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.34</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.44</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>4.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="M15" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>2.11</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2694,10 +2694,10 @@
         <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R19" t="n">
         <v>1.35</v>
@@ -2712,7 +2712,7 @@
         <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
         <v>1.13</v>
@@ -2721,10 +2721,10 @@
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.7</v>
@@ -2733,19 +2733,19 @@
         <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
         <v>1.13</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>4.06</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
         <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>4.59</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.16</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
         <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.09</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.19</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.61</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>4.61</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M29" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD29" t="n">
         <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>3.16</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>6.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1290,37 +1290,37 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>3.16</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46031.42361111111</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.19</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.92</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>4.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46031.50347222222</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.17</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.35</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.78</v>
+        <v>6.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46031.60416666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>4.59</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.09</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.19</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.25</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>4.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.44</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
         <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.71</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.61</v>
+        <v>3.31</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="T28" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.03</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O29" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>4.61</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
         <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.31</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,40 +787,40 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -832,19 +832,19 @@
         <v>3.3</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.34</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
         <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V8" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
         <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1855,10 +1855,10 @@
         <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -1873,7 +1873,7 @@
         <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
         <v>1.23</v>
@@ -1900,10 +1900,10 @@
         <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
         <v>2.28</v>
@@ -1915,7 +1915,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
         <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="P13" t="n">
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.62</v>
@@ -2016,22 +2016,22 @@
         <v>2.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
         <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
         <v>1.47</v>
@@ -2096,7 +2096,7 @@
         <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
@@ -2105,7 +2105,7 @@
         <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
         <v>2.24</v>
@@ -2123,13 +2123,13 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AA14" t="n">
         <v>2.75</v>
@@ -2138,22 +2138,22 @@
         <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="R15" t="n">
         <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="T15" t="n">
         <v>3.9</v>
@@ -2239,7 +2239,7 @@
         <v>10.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.15</v>
@@ -2257,7 +2257,7 @@
         <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.07</v>
@@ -2266,13 +2266,13 @@
         <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="n">
         <v>1.44</v>
@@ -3102,10 +3102,10 @@
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W24" t="n">
         <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
         <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
         <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
         <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,64 +3515,64 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>3.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.4</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
         <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
         <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
@@ -3581,7 +3581,7 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD27" t="n">
         <v>1.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD28" t="n">
         <v>1.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.61</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>1.94</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>3.18</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>3.71</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>4.61</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC30" t="n">
         <v>3.5</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>3.16</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>5.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>2.24</v>
@@ -1888,16 +1888,16 @@
         <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
         <v>4.6</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
         <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
         <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
         <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG14" t="n">
         <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="M15" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
         <v>4.5</v>
@@ -2245,16 +2245,16 @@
         <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
         <v>6.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>4.59</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.48</v>
       </c>
-      <c r="V21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.5</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
         <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
         <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="M25" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O25" t="n">
         <v>4</v>
       </c>
-      <c r="N25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.59</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
         <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB25" t="n">
         <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.89</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.06</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
         <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.09</v>
+        <v>3.26</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>3.8</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="AG28" t="n">
         <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>3.71</v>
       </c>
       <c r="O29" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.71</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.61</v>
+        <v>3.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>3.16</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.28</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>2.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.81</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1501,40 +1501,40 @@
         <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA9" t="n">
         <v>1.55</v>
@@ -1543,19 +1543,19 @@
         <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1620,40 +1620,40 @@
         <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA10" t="n">
         <v>1.19</v>
@@ -1662,19 +1662,19 @@
         <v>4.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="AH10" t="n">
         <v>1.01</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>2.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.17</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.35</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="M21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.59</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
         <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
         <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
         <v>1.44</v>
@@ -3102,10 +3102,10 @@
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
         <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
         <v>2.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
         <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.03</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.26</v>
+        <v>2.09</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="O28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.8</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z29" t="n">
         <v>4.1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>3.71</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.31</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>3.16</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -787,22 +787,22 @@
         <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
         <v>1.38</v>
@@ -811,7 +811,7 @@
         <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -832,19 +832,19 @@
         <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AG3" t="n">
         <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46031.23263888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.51</v>
+        <v>2.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>4.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>3.16</v>
       </c>
       <c r="T6" t="n">
-        <v>4.33</v>
+        <v>2.68</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.44</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>4.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
@@ -1290,37 +1290,37 @@
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1501,13 +1501,13 @@
         <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>4.56</v>
       </c>
       <c r="P9" t="n">
         <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
@@ -1516,25 +1516,25 @@
         <v>3.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.55</v>
@@ -1543,22 +1543,22 @@
         <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46031.38541666666</v>
@@ -1620,31 +1620,31 @@
         <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
         <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.19</v>
@@ -1674,7 +1674,7 @@
         <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AH10" t="n">
         <v>1.01</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>2.24</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>3.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>4.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.71</v>
+        <v>2.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.99</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>9.9</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.2</v>
+        <v>2.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.33</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>2.87</v>
       </c>
       <c r="M21" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
         <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
         <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="n">
         <v>1.44</v>
@@ -3102,10 +3102,10 @@
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,64 +3515,64 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>3.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.4</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
         <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC26" t="n">
         <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
@@ -3581,7 +3581,7 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S27" t="n">
         <v>2.53</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.59</v>
-      </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="M28" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.03</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC28" t="n">
         <v>4.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3890,31 +3890,31 @@
         <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U29" t="n">
         <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
         <v>1.58</v>
@@ -3929,10 +3929,10 @@
         <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AG29" t="n">
         <v>1.29</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M30" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N30" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W30" t="n">
         <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4119,25 +4119,25 @@
         <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
         <v>2.74</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
         <v>7.1</v>
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA31" t="n">
         <v>1.9</v>
@@ -4161,22 +4161,22 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AD31" t="n">
         <v>1.26</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46031.69791666666</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>1.36</v>
+        <v>2.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>4.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>3.16</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>2.68</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>6.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.05</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.28</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.63</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="M12" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.71</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V13" t="n">
-        <v>13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>3.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.95</v>
+        <v>4.46</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="AD15" t="n">
         <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
         <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>4.59</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
         <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
         <v>4.5</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>3.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="U23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.48</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.5</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.09</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.19</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.89</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC26" t="n">
         <v>2.19</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>3.24</v>
       </c>
       <c r="T27" t="n">
-        <v>2.92</v>
+        <v>2.39</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.26</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>3.71</v>
       </c>
       <c r="O29" t="n">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>3.24</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>2.39</v>
+        <v>2.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.34</v>
+        <v>1.82</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -642,39 +642,39 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="N2" t="n">
         <v>1.98</v>
       </c>
       <c r="O2" t="n">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -683,13 +683,13 @@
         <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
@@ -704,16 +704,16 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
         <v>1.72</v>
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>4.51</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="O6" t="n">
-        <v>4.05</v>
+        <v>4.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>3.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1415,31 +1415,31 @@
         <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD8" t="n">
         <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>3.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>4.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>10</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.4</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.95</v>
+        <v>4.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.33</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="M21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.59</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
         <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
         <v>2.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.89</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
         <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V23" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC23" t="n">
         <v>2.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
         <v>2.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>4.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.48</v>
       </c>
-      <c r="V25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AF25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
         <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z26" t="n">
         <v>4.5</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AA26" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -883,87 +883,87 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46031.35416666666</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="P5" t="n">
         <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.63</v>
@@ -1058,13 +1058,13 @@
         <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
         <v>6.4</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
         <v>3.2</v>
@@ -1156,13 +1156,13 @@
         <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
         <v>13</v>
@@ -1174,34 +1174,34 @@
         <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
         <v>3.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1240,27 +1240,27 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>2.25</v>
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N9" t="n">
         <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
         <v>4.8</v>
@@ -1537,28 +1537,28 @@
         <v>4.2</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AG9" t="n">
         <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46031.38541666666</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="N10" t="n">
         <v>1.08</v>
@@ -1623,31 +1623,31 @@
         <v>15.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
         <v>3.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.09</v>
@@ -1656,28 +1656,28 @@
         <v>7.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.16</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46031.41666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>6.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="M13" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.71</v>
+        <v>2.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="T13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.18</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.7</v>
+        <v>6.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>4.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AF15" t="n">
         <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.99</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2453,34 +2453,34 @@
         <v>3.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V17" t="n">
         <v>9.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
         <v>1.57</v>
@@ -2495,22 +2495,22 @@
         <v>1.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>1.77</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
         <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>2.87</v>
       </c>
       <c r="M21" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
         <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>3.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.4</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.48</v>
       </c>
-      <c r="V22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
         <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4.5</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
         <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="V24" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
         <v>4.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
         <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>2.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="O27" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>3.24</v>
+        <v>2.31</v>
       </c>
       <c r="T27" t="n">
-        <v>2.39</v>
+        <v>3.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="V27" t="n">
-        <v>5.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>4.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="AE27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3762,34 +3762,34 @@
         <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="R28" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.52</v>
@@ -3807,19 +3807,19 @@
         <v>4.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG28" t="n">
         <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3881,61 +3881,61 @@
         <v>3.71</v>
       </c>
       <c r="O29" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>3.87</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T29" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="U29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.32</v>
       </c>
-      <c r="V29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z29" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD29" t="n">
         <v>1.23</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
         <v>1.82</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.09</v>
+        <v>3.26</v>
       </c>
       <c r="M30" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>3.42</v>
+        <v>2.32</v>
       </c>
       <c r="U30" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="V30" t="n">
-        <v>9.300000000000001</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.72</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>
@@ -4122,37 +4122,37 @@
         <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
         <v>2.73</v>
       </c>
       <c r="R31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.36</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA31" t="n">
         <v>1.9</v>
@@ -4161,22 +4161,22 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD31" t="n">
         <v>1.26</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
         <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46031.69791666666</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>4.25</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>2.56</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.12</v>
+        <v>3.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>4.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.74</v>
+        <v>2.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>6.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,90 +1713,90 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
         <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46031.42361111111</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>2.58</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q12" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.64</v>
-      </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="T12" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>6.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AF12" t="n">
         <v>1.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.75</v>
+        <v>2.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>6.23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.95</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
         <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
         <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
         <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.32</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
         <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4.32</v>
       </c>
       <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
         <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
         <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46031.50347222222</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4.94</v>
+        <v>5.03</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>5.16</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46031.60416666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>3.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,68 +3035,68 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.89</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>4.06</v>
+        <v>3.82</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
         <v>2.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
@@ -3105,7 +3105,7 @@
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.58</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.9</v>
+        <v>3.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.19</v>
+        <v>3.01</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="O25" t="n">
-        <v>4.59</v>
+        <v>3.67</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.47</v>
       </c>
-      <c r="AB25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.86</v>
+        <v>3.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>4.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
         <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>2.42</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>3.87</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="U27" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>9.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>2.42</v>
+        <v>3.01</v>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.87</v>
+        <v>4.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S29" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T29" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W29" t="n">
         <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>4.47</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.74</v>
+        <v>2.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.83</v>
+        <v>6.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>2.55</v>
+        <v>3.22</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>4.47</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.13</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.55</v>
+        <v>2.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.36</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1845,77 +1845,77 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="N12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.12</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2083,77 +2083,77 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="M14" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.51</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.18</v>
       </c>
-      <c r="V14" t="n">
-        <v>12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.8</v>
+        <v>6.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2447,34 +2447,34 @@
         <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="P17" t="n">
         <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="T17" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="U17" t="n">
         <v>1.17</v>
       </c>
       <c r="V17" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -2483,25 +2483,25 @@
         <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AD17" t="n">
         <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AF17" t="n">
         <v>1.5</v>
@@ -2510,7 +2510,7 @@
         <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>1.77</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
         <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>1.86</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.77</v>
+        <v>6.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.22</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.85</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.86</v>
+        <v>1.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.25</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>3.21</v>
       </c>
       <c r="M22" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>5.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="n">
         <v>1.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="N23" t="n">
         <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.74</v>
       </c>
       <c r="P23" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
         <v>2.14</v>
@@ -3188,7 +3188,7 @@
         <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.13</v>
@@ -3209,7 +3209,7 @@
         <v>2.49</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AD23" t="n">
         <v>1.75</v>
@@ -3280,10 +3280,10 @@
         <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
         <v>2.46</v>
@@ -3292,7 +3292,7 @@
         <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>4.56</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
@@ -3316,19 +3316,19 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
         <v>3.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
         <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
         <v>1.32</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="N25" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="O25" t="n">
-        <v>3.67</v>
+        <v>4.43</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.17</v>
+        <v>4.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>3.38</v>
       </c>
       <c r="O26" t="n">
-        <v>4.59</v>
+        <v>2.56</v>
       </c>
       <c r="P26" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>3.76</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
         <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AD26" t="n">
         <v>1.53</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>3.71</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2.42</v>
+        <v>3.7</v>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.87</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>7.8</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T28" t="n">
         <v>3.05</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="U28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
         <v>3.58</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>3.58</v>
       </c>
       <c r="R30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.3</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.56</v>
-      </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC30" t="n">
         <v>4.5</v>
       </c>
-      <c r="AA30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46031.6875</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>4.47</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="U5" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.13</v>
+        <v>3.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.55</v>
+        <v>2.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.36</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>4.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.74</v>
+        <v>2.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>6.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,16 +1823,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>3.32</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.51</v>
+        <v>6.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46031.5</v>
@@ -1942,22 +1942,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.96</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.58</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.23</v>
+        <v>4.41</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="T13" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>3.32</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
         <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
         <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46031.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>4.81</v>
       </c>
       <c r="M17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.88</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2546,78 +2546,78 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
         <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
         <v>1.65</v>
@@ -2626,10 +2626,10 @@
         <v>2.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,19 +2656,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="N19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.5</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2787,17 +2787,17 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>3.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.9</v>
+        <v>5.17</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE21" t="n">
         <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.21</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z22" t="n">
         <v>4.9</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.17</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="n">
         <v>1.43</v>
@@ -3102,10 +3102,10 @@
         <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.66</v>
+        <v>3.38</v>
       </c>
       <c r="O23" t="n">
-        <v>4.74</v>
+        <v>2.56</v>
       </c>
       <c r="P23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.07</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="N25" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="O25" t="n">
-        <v>4.43</v>
+        <v>4.74</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2.49</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.48</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF25" t="n">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.94</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="N26" t="n">
-        <v>3.38</v>
+        <v>1.82</v>
       </c>
       <c r="O26" t="n">
-        <v>2.56</v>
+        <v>4.43</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.76</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="U26" t="n">
         <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="W26" t="n">
         <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3617,30 +3617,30 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
         <v>3.7</v>
@@ -3649,7 +3649,7 @@
         <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
@@ -3664,7 +3664,7 @@
         <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
         <v>1.11</v>
@@ -3676,19 +3676,19 @@
         <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE27" t="n">
         <v>1.53</v>
@@ -3700,7 +3700,7 @@
         <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,16 +3727,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.71</v>
+        <v>3.13</v>
       </c>
       <c r="O28" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S28" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="T28" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W28" t="n">
         <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,99 +3846,99 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.01</v>
+        <v>2.56</v>
       </c>
       <c r="P29" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="U29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.23</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE29" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46031.6875</v>
@@ -3974,33 +3974,33 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
         <v>1.88</v>
@@ -4009,19 +4009,19 @@
         <v>3.58</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U30" t="n">
         <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
@@ -4030,16 +4030,16 @@
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
         <v>4.5</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="O31" t="n">
         <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q31" t="n">
         <v>2.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46031.69791666666</v>
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.73</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S32" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="T32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
@@ -4268,34 +4268,34 @@
         <v>1.12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG32" t="n">
         <v>1.45</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46031.70833333334</v>

--- a/jogos_2026-01-09.xlsx
+++ b/jogos_2026-01-09.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>4.47</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.74</v>
+        <v>2.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.83</v>
+        <v>6.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46031.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,19 +1109,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46031.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46031.375</v>
@@ -1942,22 +1942,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="M13" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>2.96</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.41</v>
+        <v>2.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="S13" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.18</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.9</v>
+        <v>6.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46031.5</v>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>4.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.13</v>
       </c>
-      <c r="V14" t="n">
-        <v>11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46031.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,22 +2537,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.53</v>
+        <v>4.77</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="V18" t="n">
-        <v>5.95</v>
+        <v>9.4</v>
       </c>
       <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.07</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,23 +2656,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.77</v>
+        <v>3.53</v>
       </c>
       <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.65</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46031.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>4.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.17</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>3.21</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.9</v>
+        <v>5.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="n">
         <v>1.43</v>
@@ -3102,10 +3102,10 @@
         <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.92</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.32</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>1.66</v>
       </c>
       <c r="O24" t="n">
-        <v>2.46</v>
+        <v>4.74</v>
       </c>
       <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.56</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O25" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4.43</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="T26" t="n">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.63</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46031.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,25 +3608,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>3.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="T27" t="n">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.11</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46031.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,25 +3727,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.13</v>
+        <v>2.02</v>
       </c>
       <c r="O28" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.56</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V28" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.49</v>
+        <v>1.61</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.8</v>
+        <v>2.53</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46031.6875</v>
@@ -4093,20 +4093,20 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4212,20 +4212,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
